--- a/output/Data and Chart Outputs/europe_biomethane_operators.xlsx
+++ b/output/Data and Chart Outputs/europe_biomethane_operators.xlsx
@@ -761,7 +761,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-04 06:43 UTC</t>
+          <t>2026-10-04 06:44 UTC</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
         <v>42005</v>
       </c>
       <c r="D2" t="n">
-        <v>7.815555555555555e-05</v>
+        <v>0.07815999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -817,7 +817,7 @@
         <v>42036</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="4">
@@ -825,7 +825,7 @@
         <v>42064</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001172333333333333</v>
+        <v>0.11723</v>
       </c>
     </row>
     <row r="5">
@@ -833,7 +833,7 @@
         <v>42095</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="6">
@@ -841,7 +841,7 @@
         <v>42125</v>
       </c>
       <c r="D6" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="7">
@@ -849,7 +849,7 @@
         <v>42156</v>
       </c>
       <c r="D7" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="8">
@@ -857,7 +857,7 @@
         <v>42186</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="9">
@@ -865,7 +865,7 @@
         <v>42217</v>
       </c>
       <c r="D9" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="10">
@@ -873,7 +873,7 @@
         <v>42248</v>
       </c>
       <c r="D10" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="11">
@@ -881,7 +881,7 @@
         <v>42278</v>
       </c>
       <c r="D11" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="12">
@@ -889,7 +889,7 @@
         <v>42309</v>
       </c>
       <c r="D12" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="13">
@@ -897,7 +897,7 @@
         <v>42339</v>
       </c>
       <c r="D13" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="14">
@@ -905,7 +905,7 @@
         <v>42370</v>
       </c>
       <c r="D14" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="15">
@@ -913,7 +913,7 @@
         <v>42401</v>
       </c>
       <c r="D15" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="16">
@@ -921,7 +921,7 @@
         <v>42430</v>
       </c>
       <c r="D16" t="n">
-        <v>6.838611111111111e-05</v>
+        <v>0.06839000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -929,7 +929,7 @@
         <v>42461</v>
       </c>
       <c r="D17" t="n">
-        <v>6.838611111111111e-05</v>
+        <v>0.06839000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -937,7 +937,7 @@
         <v>42491</v>
       </c>
       <c r="D18" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="19">
@@ -945,7 +945,7 @@
         <v>42522</v>
       </c>
       <c r="D19" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="20">
@@ -953,7 +953,7 @@
         <v>42552</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001172333333333333</v>
+        <v>0.11723</v>
       </c>
     </row>
     <row r="21">
@@ -961,7 +961,7 @@
         <v>42583</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="22">
@@ -969,7 +969,7 @@
         <v>42614</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001367722222222222</v>
+        <v>0.13677</v>
       </c>
     </row>
     <row r="23">
@@ -977,7 +977,7 @@
         <v>42644</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001367722222222222</v>
+        <v>0.13677</v>
       </c>
     </row>
     <row r="24">
@@ -985,7 +985,7 @@
         <v>42675</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0001367722222222222</v>
+        <v>0.13677</v>
       </c>
     </row>
     <row r="25">
@@ -993,7 +993,7 @@
         <v>42705</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001270027777777778</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="26">
@@ -1001,7 +1001,7 @@
         <v>42736</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001953888888888889</v>
+        <v>0.19539</v>
       </c>
     </row>
     <row r="27">
@@ -1009,7 +1009,7 @@
         <v>42767</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001367722222222222</v>
+        <v>0.13677</v>
       </c>
     </row>
     <row r="28">
@@ -1017,7 +1017,7 @@
         <v>42795</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="29">
@@ -1025,7 +1025,7 @@
         <v>42826</v>
       </c>
       <c r="D29" t="n">
-        <v>7.815555555555555e-05</v>
+        <v>0.07815999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1033,7 +1033,7 @@
         <v>42856</v>
       </c>
       <c r="D30" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="31">
@@ -1041,7 +1041,7 @@
         <v>42887</v>
       </c>
       <c r="D31" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="32">
@@ -1049,7 +1049,7 @@
         <v>42917</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="33">
@@ -1057,7 +1057,7 @@
         <v>42948</v>
       </c>
       <c r="D33" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="34">
@@ -1065,7 +1065,7 @@
         <v>42979</v>
       </c>
       <c r="D34" t="n">
-        <v>9.769444444444444e-05</v>
+        <v>0.09769</v>
       </c>
     </row>
     <row r="35">
@@ -1073,7 +1073,7 @@
         <v>43009</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="36">
@@ -1081,7 +1081,7 @@
         <v>43040</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001172333333333333</v>
+        <v>0.11723</v>
       </c>
     </row>
     <row r="37">
@@ -1089,7 +1089,7 @@
         <v>43070</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0001270027777777778</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="38">
@@ -1097,7 +1097,7 @@
         <v>43101</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001367722222222222</v>
+        <v>0.13677</v>
       </c>
     </row>
     <row r="39">
@@ -1105,7 +1105,7 @@
         <v>43132</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001465416666666667</v>
+        <v>0.14654</v>
       </c>
     </row>
     <row r="40">
@@ -1113,7 +1113,7 @@
         <v>43160</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001660805555555555</v>
+        <v>0.16608</v>
       </c>
     </row>
     <row r="41">
@@ -1121,7 +1121,7 @@
         <v>43191</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001465416666666667</v>
+        <v>0.14654</v>
       </c>
     </row>
     <row r="42">
@@ -1129,7 +1129,7 @@
         <v>43221</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="43">
@@ -1137,7 +1137,7 @@
         <v>43252</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0001172333333333333</v>
+        <v>0.11723</v>
       </c>
     </row>
     <row r="44">
@@ -1145,7 +1145,7 @@
         <v>43282</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001172333333333333</v>
+        <v>0.11723</v>
       </c>
     </row>
     <row r="45">
@@ -1153,7 +1153,7 @@
         <v>43313</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0001270027777777778</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="46">
@@ -1161,7 +1161,7 @@
         <v>43344</v>
       </c>
       <c r="D46" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="47">
@@ -1169,7 +1169,7 @@
         <v>43374</v>
       </c>
       <c r="D47" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="48">
@@ -1177,7 +1177,7 @@
         <v>43405</v>
       </c>
       <c r="D48" t="n">
-        <v>8.792500000000001e-05</v>
+        <v>0.08792</v>
       </c>
     </row>
     <row r="49">
@@ -1185,7 +1185,7 @@
         <v>43435</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0001074638888888889</v>
+        <v>0.10746</v>
       </c>
     </row>
     <row r="50">
@@ -1193,7 +1193,7 @@
         <v>43466</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001563111111111111</v>
+        <v>0.15631</v>
       </c>
     </row>
     <row r="51">
@@ -1201,7 +1201,7 @@
         <v>43497</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0001367722222222222</v>
+        <v>0.13677</v>
       </c>
     </row>
     <row r="52">
@@ -1209,7 +1209,7 @@
         <v>43525</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0001563111111111111</v>
+        <v>0.15631</v>
       </c>
     </row>
     <row r="53">
@@ -1217,7 +1217,7 @@
         <v>43556</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0001465416666666667</v>
+        <v>0.14654</v>
       </c>
     </row>
     <row r="54">
@@ -1225,7 +1225,7 @@
         <v>43586</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0001856194444444444</v>
+        <v>0.18562</v>
       </c>
     </row>
     <row r="55">
@@ -1233,7 +1233,7 @@
         <v>43617</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0001563111111111111</v>
+        <v>0.15631</v>
       </c>
     </row>
     <row r="56">
@@ -1241,7 +1241,7 @@
         <v>43647</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0001465416666666667</v>
+        <v>0.14654</v>
       </c>
     </row>
     <row r="57">
@@ -1249,7 +1249,7 @@
         <v>43678</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0001465416666666667</v>
+        <v>0.14654</v>
       </c>
     </row>
     <row r="58">
@@ -1257,7 +1257,7 @@
         <v>43709</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0001367722222222222</v>
+        <v>0.13677</v>
       </c>
     </row>
     <row r="59">
@@ -1265,7 +1265,7 @@
         <v>43739</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0001465416666666667</v>
+        <v>0.14654</v>
       </c>
     </row>
     <row r="60">
@@ -1273,7 +1273,7 @@
         <v>43770</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0001563111111111111</v>
+        <v>0.15631</v>
       </c>
     </row>
     <row r="61">
@@ -1281,7 +1281,7 @@
         <v>43800</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0001563111111111111</v>
+        <v>0.15631</v>
       </c>
     </row>
     <row r="62">
@@ -1295,7 +1295,7 @@
         <v>0.30019</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0001953888888888889</v>
+        <v>0.19539</v>
       </c>
     </row>
     <row r="63">
@@ -1309,7 +1309,7 @@
         <v>0.299234</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0001953888888888889</v>
+        <v>0.19539</v>
       </c>
     </row>
     <row r="64">
@@ -1323,7 +1323,7 @@
         <v>0.331915</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0001953888888888889</v>
+        <v>0.19539</v>
       </c>
     </row>
     <row r="65">
@@ -1337,7 +1337,7 @@
         <v>0.336595</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0001856194444444444</v>
+        <v>0.18562</v>
       </c>
     </row>
     <row r="66">
@@ -1351,7 +1351,7 @@
         <v>0.34386</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0001953888888888889</v>
+        <v>0.19539</v>
       </c>
     </row>
     <row r="67">
@@ -1365,7 +1365,7 @@
         <v>0.323476</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0002051583333333333</v>
+        <v>0.20516</v>
       </c>
     </row>
     <row r="68">
@@ -1379,7 +1379,7 @@
         <v>0.354709</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0002051583333333333</v>
+        <v>0.20516</v>
       </c>
     </row>
     <row r="69">
@@ -1393,7 +1393,7 @@
         <v>0.378345</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0002051583333333333</v>
+        <v>0.20516</v>
       </c>
     </row>
     <row r="70">
@@ -1407,7 +1407,7 @@
         <v>0.396682</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0002246972222222222</v>
+        <v>0.2247</v>
       </c>
     </row>
     <row r="71">
@@ -1421,7 +1421,7 @@
         <v>0.439452</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0002051583333333333</v>
+        <v>0.20516</v>
       </c>
     </row>
     <row r="72">
@@ -1435,7 +1435,7 @@
         <v>0.453377</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0002051583333333333</v>
+        <v>0.20516</v>
       </c>
     </row>
     <row r="73">
@@ -1449,7 +1449,7 @@
         <v>0.470401</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0002051583333333333</v>
+        <v>0.20516</v>
       </c>
     </row>
     <row r="74">
@@ -1463,7 +1463,7 @@
         <v>0.472205</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0002149277777777778</v>
+        <v>0.21493</v>
       </c>
     </row>
     <row r="75">
@@ -1477,7 +1477,7 @@
         <v>0.43402</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0002051583333333333</v>
+        <v>0.20516</v>
       </c>
     </row>
     <row r="76">
@@ -1491,7 +1491,7 @@
         <v>0.489866</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0001856194444444444</v>
+        <v>0.18562</v>
       </c>
     </row>
     <row r="77">
@@ -1505,7 +1505,7 @@
         <v>0.469215</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0001856194444444444</v>
+        <v>0.18562</v>
       </c>
     </row>
     <row r="78">
@@ -1519,7 +1519,7 @@
         <v>0.492307</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0002246972222222222</v>
+        <v>0.2247</v>
       </c>
     </row>
     <row r="79">
@@ -1533,7 +1533,7 @@
         <v>0.472076</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0002442361111111111</v>
+        <v>0.24424</v>
       </c>
     </row>
     <row r="80">
@@ -1547,7 +1547,7 @@
         <v>0.496042</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0002344666666666666</v>
+        <v>0.23447</v>
       </c>
     </row>
     <row r="81">
@@ -1561,7 +1561,7 @@
         <v>0.5279940000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0002344666666666666</v>
+        <v>0.23447</v>
       </c>
     </row>
     <row r="82">
@@ -1575,7 +1575,7 @@
         <v>0.504895</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0002051583333333333</v>
+        <v>0.20516</v>
       </c>
     </row>
     <row r="83">
@@ -1589,7 +1589,7 @@
         <v>0.549749</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0002344666666666666</v>
+        <v>0.23447</v>
       </c>
     </row>
     <row r="84">
@@ -1603,7 +1603,7 @@
         <v>0.553173</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0002149277777777778</v>
+        <v>0.21493</v>
       </c>
     </row>
     <row r="85">
@@ -1617,7 +1617,7 @@
         <v>0.5778799999999999</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0002246972222222222</v>
+        <v>0.2247</v>
       </c>
     </row>
     <row r="86">
@@ -1631,7 +1631,7 @@
         <v>0.563333</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0002833138888888889</v>
+        <v>0.28331</v>
       </c>
     </row>
     <row r="87">
@@ -1645,7 +1645,7 @@
         <v>0.509483</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0002540055555555555</v>
+        <v>0.25401</v>
       </c>
     </row>
     <row r="88">
@@ -1659,7 +1659,7 @@
         <v>0.565313</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0003419305555555555</v>
+        <v>0.34193</v>
       </c>
     </row>
     <row r="89">
@@ -1673,7 +1673,7 @@
         <v>0.532794</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0002930833333333333</v>
+        <v>0.29308</v>
       </c>
     </row>
     <row r="90">
@@ -1687,7 +1687,7 @@
         <v>0.544442</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0003126222222222222</v>
+        <v>0.31262</v>
       </c>
     </row>
     <row r="91">
@@ -1701,7 +1701,7 @@
         <v>0.5375650000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0002930833333333333</v>
+        <v>0.29308</v>
       </c>
     </row>
     <row r="92">
@@ -1715,7 +1715,7 @@
         <v>0.561101</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0003419305555555555</v>
+        <v>0.34193</v>
       </c>
     </row>
     <row r="93">
@@ -1729,7 +1729,7 @@
         <v>0.5787340000000001</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0003712388888888889</v>
+        <v>0.37124</v>
       </c>
     </row>
     <row r="94">
@@ -1743,7 +1743,7 @@
         <v>0.613546</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0003223916666666666</v>
+        <v>0.32239</v>
       </c>
     </row>
     <row r="95">
@@ -1757,7 +1757,7 @@
         <v>0.677276</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0002735444444444444</v>
+        <v>0.27354</v>
       </c>
     </row>
     <row r="96">
@@ -1771,7 +1771,7 @@
         <v>0.636254</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0002735444444444444</v>
+        <v>0.27354</v>
       </c>
     </row>
     <row r="97">
@@ -1785,7 +1785,7 @@
         <v>0.6465080000000001</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0003126222222222222</v>
+        <v>0.31262</v>
       </c>
     </row>
     <row r="98">
@@ -1799,7 +1799,7 @@
         <v>0.679295</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0002930833333333333</v>
+        <v>0.29308</v>
       </c>
     </row>
     <row r="99">
@@ -1813,7 +1813,7 @@
         <v>0.5947749999999999</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0002735444444444444</v>
+        <v>0.27354</v>
       </c>
     </row>
     <row r="100">
@@ -1827,7 +1827,7 @@
         <v>0.663173</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0002833138888888889</v>
+        <v>0.28331</v>
       </c>
     </row>
     <row r="101">
@@ -1841,7 +1841,7 @@
         <v>0.657393</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0002833138888888889</v>
+        <v>0.28331</v>
       </c>
     </row>
     <row r="102">
@@ -1855,7 +1855,7 @@
         <v>0.686952</v>
       </c>
       <c r="D102" t="n">
-        <v>0.0003028527777777777</v>
+        <v>0.30285</v>
       </c>
     </row>
     <row r="103">
@@ -1869,7 +1869,7 @@
         <v>0.6564800000000001</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0002833138888888889</v>
+        <v>0.28331</v>
       </c>
     </row>
     <row r="104">
@@ -1883,7 +1883,7 @@
         <v>0.6743089999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0002930833333333333</v>
+        <v>0.29308</v>
       </c>
     </row>
     <row r="105">
@@ -1897,7 +1897,7 @@
         <v>0.679042</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0003126222222222222</v>
+        <v>0.31262</v>
       </c>
     </row>
     <row r="106">
@@ -1911,7 +1911,7 @@
         <v>0.6652830000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>0.0003126222222222222</v>
+        <v>0.31262</v>
       </c>
     </row>
     <row r="107">
@@ -1925,7 +1925,7 @@
         <v>0.7005739999999999</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0002930833333333333</v>
+        <v>0.29308</v>
       </c>
     </row>
     <row r="108">
@@ -1939,7 +1939,7 @@
         <v>0.664866</v>
       </c>
       <c r="D108" t="n">
-        <v>0.000263775</v>
+        <v>0.26377</v>
       </c>
     </row>
     <row r="109">
@@ -1953,7 +1953,7 @@
         <v>0.664649</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0002833138888888889</v>
+        <v>0.28331</v>
       </c>
     </row>
     <row r="110">
@@ -1967,7 +1967,7 @@
         <v>0.6899</v>
       </c>
       <c r="D110" t="n">
-        <v>0.0003028527777777777</v>
+        <v>0.30285</v>
       </c>
     </row>
     <row r="111">
@@ -1981,7 +1981,7 @@
         <v>0.6412340000000001</v>
       </c>
       <c r="D111" t="n">
-        <v>0.000263775</v>
+        <v>0.26377</v>
       </c>
     </row>
     <row r="112">
@@ -1995,7 +1995,7 @@
         <v>0.692534</v>
       </c>
       <c r="D112" t="n">
-        <v>0.000263775</v>
+        <v>0.26377</v>
       </c>
     </row>
     <row r="113">
@@ -2009,7 +2009,7 @@
         <v>0.654726</v>
       </c>
       <c r="D113" t="n">
-        <v>0.0002540055555555555</v>
+        <v>0.25401</v>
       </c>
     </row>
     <row r="114">
@@ -2023,7 +2023,7 @@
         <v>0.6708999999999999</v>
       </c>
       <c r="D114" t="n">
-        <v>0.000263775</v>
+        <v>0.26377</v>
       </c>
     </row>
     <row r="115">
@@ -2037,7 +2037,7 @@
         <v>0.6483239999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>0.0003028527777777777</v>
+        <v>0.30285</v>
       </c>
     </row>
     <row r="116">
@@ -2051,7 +2051,7 @@
         <v>0.665036</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0003126222222222222</v>
+        <v>0.31262</v>
       </c>
     </row>
     <row r="117">
@@ -2065,7 +2065,7 @@
         <v>0.6824199999999999</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0003223916666666666</v>
+        <v>0.32239</v>
       </c>
     </row>
     <row r="118">
@@ -2079,7 +2079,7 @@
         <v>0.678015</v>
       </c>
       <c r="D118" t="n">
-        <v>0.0003028527777777777</v>
+        <v>0.30285</v>
       </c>
     </row>
     <row r="119">
@@ -2093,7 +2093,7 @@
         <v>0.70621</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0003223916666666666</v>
+        <v>0.32239</v>
       </c>
     </row>
     <row r="120">
@@ -2107,7 +2107,7 @@
         <v>0.6968840000000001</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0003028527777777777</v>
+        <v>0.30285</v>
       </c>
     </row>
     <row r="121">
@@ -2121,7 +2121,7 @@
         <v>0.723257</v>
       </c>
       <c r="D121" t="n">
-        <v>0.0003321611111111111</v>
+        <v>0.33216</v>
       </c>
     </row>
     <row r="122">
@@ -2135,7 +2135,7 @@
         <v>0.7921699999999999</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0003810083333333333</v>
+        <v>0.38101</v>
       </c>
     </row>
     <row r="123">
@@ -2149,7 +2149,7 @@
         <v>0.663165</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0003419305555555555</v>
+        <v>0.34193</v>
       </c>
     </row>
     <row r="124">
@@ -2163,7 +2163,7 @@
         <v>0.744068</v>
       </c>
       <c r="D124" t="n">
-        <v>0.0003810083333333333</v>
+        <v>0.38101</v>
       </c>
     </row>
     <row r="125">
@@ -2177,7 +2177,7 @@
         <v>0.7054279999999999</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0003614694444444445</v>
+        <v>0.36147</v>
       </c>
     </row>
     <row r="126">
@@ -2191,7 +2191,7 @@
         <v>0.7255470000000001</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0004200861111111111</v>
+        <v>0.42009</v>
       </c>
     </row>
     <row r="127">
@@ -2205,7 +2205,7 @@
         <v>0.675714</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0003810083333333333</v>
+        <v>0.38101</v>
       </c>
     </row>
     <row r="128">
@@ -2219,7 +2219,7 @@
         <v>0.6614679999999999</v>
       </c>
       <c r="D128" t="n">
-        <v>0.0004005472222222222</v>
+        <v>0.40055</v>
       </c>
     </row>
     <row r="129">
@@ -2233,7 +2233,7 @@
         <v>0.670311</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0003907777777777778</v>
+        <v>0.39078</v>
       </c>
     </row>
     <row r="130">
@@ -2247,7 +2247,7 @@
         <v>0.6625700000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>0.0003614694444444445</v>
+        <v>0.36147</v>
       </c>
     </row>
     <row r="131">
@@ -2261,7 +2261,7 @@
         <v>0.691119</v>
       </c>
       <c r="D131" t="n">
-        <v>0.0003712388888888889</v>
+        <v>0.37124</v>
       </c>
     </row>
     <row r="132">
@@ -2275,7 +2275,7 @@
         <v>0.661785</v>
       </c>
       <c r="D132" t="n">
-        <v>0.0003712388888888889</v>
+        <v>0.37124</v>
       </c>
     </row>
     <row r="133">
@@ -2289,7 +2289,7 @@
         <v>0.684659</v>
       </c>
       <c r="D133" t="n">
-        <v>0.0003810083333333333</v>
+        <v>0.38101</v>
       </c>
     </row>
     <row r="134">
@@ -2303,7 +2303,7 @@
         <v>0.6745890000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0003712388888888889</v>
+        <v>0.37124</v>
       </c>
     </row>
     <row r="135">
@@ -2317,7 +2317,7 @@
         <v>0.634038</v>
       </c>
       <c r="D135" t="n">
-        <v>0.0003419305555555555</v>
+        <v>0.34193</v>
       </c>
     </row>
     <row r="136">
@@ -2331,7 +2331,7 @@
         <v>0.743146</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0004103166666666667</v>
+        <v>0.41032</v>
       </c>
     </row>
     <row r="137">
@@ -2345,7 +2345,7 @@
         <v>0.7226359999999999</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0003712388888888889</v>
+        <v>0.37124</v>
       </c>
     </row>
     <row r="138">
@@ -2359,7 +2359,7 @@
         <v>0.757698</v>
       </c>
       <c r="D138" t="n">
-        <v>0.0004005472222222222</v>
+        <v>0.40055</v>
       </c>
     </row>
     <row r="139">
@@ -2373,7 +2373,7 @@
         <v>0.7310399999999999</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0003907777777777778</v>
+        <v>0.39078</v>
       </c>
     </row>
     <row r="140">
@@ -2387,7 +2387,7 @@
         <v>0.7862210000000001</v>
       </c>
       <c r="D140" t="n">
-        <v>0.0004103166666666667</v>
+        <v>0.41032</v>
       </c>
     </row>
     <row r="141">
@@ -2401,7 +2401,7 @@
         <v>0.768591</v>
       </c>
       <c r="D141" t="n">
-        <v>0.0003810083333333333</v>
+        <v>0.38101</v>
       </c>
     </row>
     <row r="142">
@@ -29620,7 +29620,7 @@
         <v>42005</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07815555555555555</v>
+        <v>78.16</v>
       </c>
     </row>
     <row r="3">
@@ -29628,7 +29628,7 @@
         <v>42036</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="4">
@@ -29636,7 +29636,7 @@
         <v>42064</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1172333333333333</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="5">
@@ -29644,7 +29644,7 @@
         <v>42095</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="6">
@@ -29652,7 +29652,7 @@
         <v>42125</v>
       </c>
       <c r="B6" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="7">
@@ -29660,7 +29660,7 @@
         <v>42156</v>
       </c>
       <c r="B7" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="8">
@@ -29668,7 +29668,7 @@
         <v>42186</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="9">
@@ -29676,7 +29676,7 @@
         <v>42217</v>
       </c>
       <c r="B9" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="10">
@@ -29684,7 +29684,7 @@
         <v>42248</v>
       </c>
       <c r="B10" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="11">
@@ -29692,7 +29692,7 @@
         <v>42278</v>
       </c>
       <c r="B11" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="12">
@@ -29700,7 +29700,7 @@
         <v>42309</v>
       </c>
       <c r="B12" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="13">
@@ -29708,7 +29708,7 @@
         <v>42339</v>
       </c>
       <c r="B13" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="14">
@@ -29716,7 +29716,7 @@
         <v>42370</v>
       </c>
       <c r="B14" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="15">
@@ -29724,7 +29724,7 @@
         <v>42401</v>
       </c>
       <c r="B15" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="16">
@@ -29732,7 +29732,7 @@
         <v>42430</v>
       </c>
       <c r="B16" t="n">
-        <v>0.06838611111111111</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="17">
@@ -29740,7 +29740,7 @@
         <v>42461</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06838611111111111</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="18">
@@ -29748,7 +29748,7 @@
         <v>42491</v>
       </c>
       <c r="B18" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="19">
@@ -29756,7 +29756,7 @@
         <v>42522</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="20">
@@ -29764,7 +29764,7 @@
         <v>42552</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1172333333333333</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="21">
@@ -29772,7 +29772,7 @@
         <v>42583</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="22">
@@ -29780,7 +29780,7 @@
         <v>42614</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1367722222222222</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="23">
@@ -29788,7 +29788,7 @@
         <v>42644</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1367722222222222</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="24">
@@ -29796,7 +29796,7 @@
         <v>42675</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1367722222222222</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="25">
@@ -29804,7 +29804,7 @@
         <v>42705</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1270027777777778</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26">
@@ -29812,7 +29812,7 @@
         <v>42736</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1953888888888889</v>
+        <v>195.39</v>
       </c>
     </row>
     <row r="27">
@@ -29820,7 +29820,7 @@
         <v>42767</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1367722222222222</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="28">
@@ -29828,7 +29828,7 @@
         <v>42795</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="29">
@@ -29836,7 +29836,7 @@
         <v>42826</v>
       </c>
       <c r="B29" t="n">
-        <v>0.07815555555555555</v>
+        <v>78.16</v>
       </c>
     </row>
     <row r="30">
@@ -29844,7 +29844,7 @@
         <v>42856</v>
       </c>
       <c r="B30" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="31">
@@ -29852,7 +29852,7 @@
         <v>42887</v>
       </c>
       <c r="B31" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="32">
@@ -29860,7 +29860,7 @@
         <v>42917</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="33">
@@ -29868,7 +29868,7 @@
         <v>42948</v>
       </c>
       <c r="B33" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="34">
@@ -29876,7 +29876,7 @@
         <v>42979</v>
       </c>
       <c r="B34" t="n">
-        <v>0.09769444444444444</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="35">
@@ -29884,7 +29884,7 @@
         <v>43009</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="36">
@@ -29892,7 +29892,7 @@
         <v>43040</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1172333333333333</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="37">
@@ -29900,7 +29900,7 @@
         <v>43070</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1270027777777778</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38">
@@ -29908,7 +29908,7 @@
         <v>43101</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1367722222222222</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="39">
@@ -29916,7 +29916,7 @@
         <v>43132</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1465416666666667</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="40">
@@ -29924,7 +29924,7 @@
         <v>43160</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1660805555555555</v>
+        <v>166.08</v>
       </c>
     </row>
     <row r="41">
@@ -29932,7 +29932,7 @@
         <v>43191</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1465416666666667</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="42">
@@ -29940,7 +29940,7 @@
         <v>43221</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="43">
@@ -29948,7 +29948,7 @@
         <v>43252</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1172333333333333</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="44">
@@ -29956,7 +29956,7 @@
         <v>43282</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1172333333333333</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="45">
@@ -29964,7 +29964,7 @@
         <v>43313</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1270027777777778</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46">
@@ -29972,7 +29972,7 @@
         <v>43344</v>
       </c>
       <c r="B46" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="47">
@@ -29980,7 +29980,7 @@
         <v>43374</v>
       </c>
       <c r="B47" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="48">
@@ -29988,7 +29988,7 @@
         <v>43405</v>
       </c>
       <c r="B48" t="n">
-        <v>0.087925</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="49">
@@ -29996,7 +29996,7 @@
         <v>43435</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1074638888888889</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="50">
@@ -30004,7 +30004,7 @@
         <v>43466</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1563111111111111</v>
+        <v>156.31</v>
       </c>
     </row>
     <row r="51">
@@ -30012,7 +30012,7 @@
         <v>43497</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1367722222222222</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="52">
@@ -30020,7 +30020,7 @@
         <v>43525</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1563111111111111</v>
+        <v>156.31</v>
       </c>
     </row>
     <row r="53">
@@ -30028,7 +30028,7 @@
         <v>43556</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1465416666666667</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="54">
@@ -30036,7 +30036,7 @@
         <v>43586</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1856194444444444</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="55">
@@ -30044,7 +30044,7 @@
         <v>43617</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1563111111111111</v>
+        <v>156.31</v>
       </c>
     </row>
     <row r="56">
@@ -30052,7 +30052,7 @@
         <v>43647</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1465416666666667</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="57">
@@ -30060,7 +30060,7 @@
         <v>43678</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1465416666666667</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="58">
@@ -30068,7 +30068,7 @@
         <v>43709</v>
       </c>
       <c r="B58" t="n">
-        <v>0.1367722222222222</v>
+        <v>136.77</v>
       </c>
     </row>
     <row r="59">
@@ -30076,7 +30076,7 @@
         <v>43739</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1465416666666667</v>
+        <v>146.54</v>
       </c>
     </row>
     <row r="60">
@@ -30084,7 +30084,7 @@
         <v>43770</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1563111111111111</v>
+        <v>156.31</v>
       </c>
     </row>
     <row r="61">
@@ -30092,7 +30092,7 @@
         <v>43800</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1563111111111111</v>
+        <v>156.31</v>
       </c>
     </row>
     <row r="62">
@@ -30100,7 +30100,7 @@
         <v>43831</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1953888888888889</v>
+        <v>195.39</v>
       </c>
     </row>
     <row r="63">
@@ -30108,7 +30108,7 @@
         <v>43862</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1953888888888889</v>
+        <v>195.39</v>
       </c>
     </row>
     <row r="64">
@@ -30116,7 +30116,7 @@
         <v>43891</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1953888888888889</v>
+        <v>195.39</v>
       </c>
     </row>
     <row r="65">
@@ -30124,7 +30124,7 @@
         <v>43922</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1856194444444444</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="66">
@@ -30132,7 +30132,7 @@
         <v>43952</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1953888888888889</v>
+        <v>195.39</v>
       </c>
     </row>
     <row r="67">
@@ -30140,7 +30140,7 @@
         <v>43983</v>
       </c>
       <c r="B67" t="n">
-        <v>0.2051583333333333</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="68">
@@ -30148,7 +30148,7 @@
         <v>44013</v>
       </c>
       <c r="B68" t="n">
-        <v>0.2051583333333333</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="69">
@@ -30156,7 +30156,7 @@
         <v>44044</v>
       </c>
       <c r="B69" t="n">
-        <v>0.2051583333333333</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="70">
@@ -30164,7 +30164,7 @@
         <v>44075</v>
       </c>
       <c r="B70" t="n">
-        <v>0.2246972222222222</v>
+        <v>224.7</v>
       </c>
     </row>
     <row r="71">
@@ -30172,7 +30172,7 @@
         <v>44105</v>
       </c>
       <c r="B71" t="n">
-        <v>0.2051583333333333</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="72">
@@ -30180,7 +30180,7 @@
         <v>44136</v>
       </c>
       <c r="B72" t="n">
-        <v>0.2051583333333333</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="73">
@@ -30188,7 +30188,7 @@
         <v>44166</v>
       </c>
       <c r="B73" t="n">
-        <v>0.2051583333333333</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="74">
@@ -30196,7 +30196,7 @@
         <v>44197</v>
       </c>
       <c r="B74" t="n">
-        <v>0.2149277777777778</v>
+        <v>214.93</v>
       </c>
     </row>
     <row r="75">
@@ -30204,7 +30204,7 @@
         <v>44228</v>
       </c>
       <c r="B75" t="n">
-        <v>0.2051583333333333</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="76">
@@ -30212,7 +30212,7 @@
         <v>44256</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1856194444444444</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="77">
@@ -30220,7 +30220,7 @@
         <v>44287</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1856194444444444</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="78">
@@ -30228,7 +30228,7 @@
         <v>44317</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2246972222222222</v>
+        <v>224.7</v>
       </c>
     </row>
     <row r="79">
@@ -30236,7 +30236,7 @@
         <v>44348</v>
       </c>
       <c r="B79" t="n">
-        <v>0.2442361111111111</v>
+        <v>244.24</v>
       </c>
     </row>
     <row r="80">
@@ -30244,7 +30244,7 @@
         <v>44378</v>
       </c>
       <c r="B80" t="n">
-        <v>0.2344666666666666</v>
+        <v>234.47</v>
       </c>
     </row>
     <row r="81">
@@ -30252,7 +30252,7 @@
         <v>44409</v>
       </c>
       <c r="B81" t="n">
-        <v>0.2344666666666666</v>
+        <v>234.47</v>
       </c>
     </row>
     <row r="82">
@@ -30260,7 +30260,7 @@
         <v>44440</v>
       </c>
       <c r="B82" t="n">
-        <v>0.2051583333333333</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="83">
@@ -30268,7 +30268,7 @@
         <v>44470</v>
       </c>
       <c r="B83" t="n">
-        <v>0.2344666666666666</v>
+        <v>234.47</v>
       </c>
     </row>
     <row r="84">
@@ -30276,7 +30276,7 @@
         <v>44501</v>
       </c>
       <c r="B84" t="n">
-        <v>0.2149277777777778</v>
+        <v>214.93</v>
       </c>
     </row>
     <row r="85">
@@ -30284,7 +30284,7 @@
         <v>44531</v>
       </c>
       <c r="B85" t="n">
-        <v>0.2246972222222222</v>
+        <v>224.7</v>
       </c>
     </row>
     <row r="86">
@@ -30292,7 +30292,7 @@
         <v>44562</v>
       </c>
       <c r="B86" t="n">
-        <v>0.2833138888888889</v>
+        <v>283.31</v>
       </c>
     </row>
     <row r="87">
@@ -30300,7 +30300,7 @@
         <v>44593</v>
       </c>
       <c r="B87" t="n">
-        <v>0.2540055555555555</v>
+        <v>254.01</v>
       </c>
     </row>
     <row r="88">
@@ -30308,7 +30308,7 @@
         <v>44621</v>
       </c>
       <c r="B88" t="n">
-        <v>0.3419305555555555</v>
+        <v>341.93</v>
       </c>
     </row>
     <row r="89">
@@ -30316,7 +30316,7 @@
         <v>44652</v>
       </c>
       <c r="B89" t="n">
-        <v>0.2930833333333333</v>
+        <v>293.08</v>
       </c>
     </row>
     <row r="90">
@@ -30324,7 +30324,7 @@
         <v>44682</v>
       </c>
       <c r="B90" t="n">
-        <v>0.3126222222222222</v>
+        <v>312.62</v>
       </c>
     </row>
     <row r="91">
@@ -30332,7 +30332,7 @@
         <v>44713</v>
       </c>
       <c r="B91" t="n">
-        <v>0.2930833333333333</v>
+        <v>293.08</v>
       </c>
     </row>
     <row r="92">
@@ -30340,7 +30340,7 @@
         <v>44743</v>
       </c>
       <c r="B92" t="n">
-        <v>0.3419305555555555</v>
+        <v>341.93</v>
       </c>
     </row>
     <row r="93">
@@ -30348,7 +30348,7 @@
         <v>44774</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3712388888888889</v>
+        <v>371.24</v>
       </c>
     </row>
     <row r="94">
@@ -30356,7 +30356,7 @@
         <v>44805</v>
       </c>
       <c r="B94" t="n">
-        <v>0.3223916666666666</v>
+        <v>322.39</v>
       </c>
     </row>
     <row r="95">
@@ -30364,7 +30364,7 @@
         <v>44835</v>
       </c>
       <c r="B95" t="n">
-        <v>0.2735444444444444</v>
+        <v>273.54</v>
       </c>
     </row>
     <row r="96">
@@ -30372,7 +30372,7 @@
         <v>44866</v>
       </c>
       <c r="B96" t="n">
-        <v>0.2735444444444444</v>
+        <v>273.54</v>
       </c>
     </row>
     <row r="97">
@@ -30380,7 +30380,7 @@
         <v>44896</v>
       </c>
       <c r="B97" t="n">
-        <v>0.3126222222222222</v>
+        <v>312.62</v>
       </c>
     </row>
     <row r="98">
@@ -30388,7 +30388,7 @@
         <v>44927</v>
       </c>
       <c r="B98" t="n">
-        <v>0.2930833333333333</v>
+        <v>293.08</v>
       </c>
     </row>
     <row r="99">
@@ -30396,7 +30396,7 @@
         <v>44958</v>
       </c>
       <c r="B99" t="n">
-        <v>0.2735444444444444</v>
+        <v>273.54</v>
       </c>
     </row>
     <row r="100">
@@ -30404,7 +30404,7 @@
         <v>44986</v>
       </c>
       <c r="B100" t="n">
-        <v>0.2833138888888889</v>
+        <v>283.31</v>
       </c>
     </row>
     <row r="101">
@@ -30412,7 +30412,7 @@
         <v>45017</v>
       </c>
       <c r="B101" t="n">
-        <v>0.2833138888888889</v>
+        <v>283.31</v>
       </c>
     </row>
     <row r="102">
@@ -30420,7 +30420,7 @@
         <v>45047</v>
       </c>
       <c r="B102" t="n">
-        <v>0.3028527777777777</v>
+        <v>302.85</v>
       </c>
     </row>
     <row r="103">
@@ -30428,7 +30428,7 @@
         <v>45078</v>
       </c>
       <c r="B103" t="n">
-        <v>0.2833138888888889</v>
+        <v>283.31</v>
       </c>
     </row>
     <row r="104">
@@ -30436,7 +30436,7 @@
         <v>45108</v>
       </c>
       <c r="B104" t="n">
-        <v>0.2930833333333333</v>
+        <v>293.08</v>
       </c>
     </row>
     <row r="105">
@@ -30444,7 +30444,7 @@
         <v>45139</v>
       </c>
       <c r="B105" t="n">
-        <v>0.3126222222222222</v>
+        <v>312.62</v>
       </c>
     </row>
     <row r="106">
@@ -30452,7 +30452,7 @@
         <v>45170</v>
       </c>
       <c r="B106" t="n">
-        <v>0.3126222222222222</v>
+        <v>312.62</v>
       </c>
     </row>
     <row r="107">
@@ -30460,7 +30460,7 @@
         <v>45200</v>
       </c>
       <c r="B107" t="n">
-        <v>0.2930833333333333</v>
+        <v>293.08</v>
       </c>
     </row>
     <row r="108">
@@ -30468,7 +30468,7 @@
         <v>45231</v>
       </c>
       <c r="B108" t="n">
-        <v>0.263775</v>
+        <v>263.77</v>
       </c>
     </row>
     <row r="109">
@@ -30476,7 +30476,7 @@
         <v>45261</v>
       </c>
       <c r="B109" t="n">
-        <v>0.2833138888888889</v>
+        <v>283.31</v>
       </c>
     </row>
     <row r="110">
@@ -30484,7 +30484,7 @@
         <v>45292</v>
       </c>
       <c r="B110" t="n">
-        <v>0.3028527777777777</v>
+        <v>302.85</v>
       </c>
     </row>
     <row r="111">
@@ -30492,7 +30492,7 @@
         <v>45323</v>
       </c>
       <c r="B111" t="n">
-        <v>0.263775</v>
+        <v>263.77</v>
       </c>
     </row>
     <row r="112">
@@ -30500,7 +30500,7 @@
         <v>45352</v>
       </c>
       <c r="B112" t="n">
-        <v>0.263775</v>
+        <v>263.77</v>
       </c>
     </row>
     <row r="113">
@@ -30508,7 +30508,7 @@
         <v>45383</v>
       </c>
       <c r="B113" t="n">
-        <v>0.2540055555555555</v>
+        <v>254.01</v>
       </c>
     </row>
     <row r="114">
@@ -30516,7 +30516,7 @@
         <v>45413</v>
       </c>
       <c r="B114" t="n">
-        <v>0.263775</v>
+        <v>263.77</v>
       </c>
     </row>
     <row r="115">
@@ -30524,7 +30524,7 @@
         <v>45444</v>
       </c>
       <c r="B115" t="n">
-        <v>0.3028527777777777</v>
+        <v>302.85</v>
       </c>
     </row>
     <row r="116">
@@ -30532,7 +30532,7 @@
         <v>45474</v>
       </c>
       <c r="B116" t="n">
-        <v>0.3126222222222222</v>
+        <v>312.62</v>
       </c>
     </row>
     <row r="117">
@@ -30540,7 +30540,7 @@
         <v>45505</v>
       </c>
       <c r="B117" t="n">
-        <v>0.3223916666666666</v>
+        <v>322.39</v>
       </c>
     </row>
     <row r="118">
@@ -30548,7 +30548,7 @@
         <v>45536</v>
       </c>
       <c r="B118" t="n">
-        <v>0.3028527777777777</v>
+        <v>302.85</v>
       </c>
     </row>
     <row r="119">
@@ -30556,7 +30556,7 @@
         <v>45566</v>
       </c>
       <c r="B119" t="n">
-        <v>0.3223916666666666</v>
+        <v>322.39</v>
       </c>
     </row>
     <row r="120">
@@ -30564,7 +30564,7 @@
         <v>45597</v>
       </c>
       <c r="B120" t="n">
-        <v>0.3028527777777777</v>
+        <v>302.85</v>
       </c>
     </row>
     <row r="121">
@@ -30572,7 +30572,7 @@
         <v>45627</v>
       </c>
       <c r="B121" t="n">
-        <v>0.3321611111111111</v>
+        <v>332.16</v>
       </c>
     </row>
     <row r="122">
@@ -30580,7 +30580,7 @@
         <v>45658</v>
       </c>
       <c r="B122" t="n">
-        <v>0.3810083333333333</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="123">
@@ -30588,7 +30588,7 @@
         <v>45689</v>
       </c>
       <c r="B123" t="n">
-        <v>0.3419305555555555</v>
+        <v>341.93</v>
       </c>
     </row>
     <row r="124">
@@ -30596,7 +30596,7 @@
         <v>45717</v>
       </c>
       <c r="B124" t="n">
-        <v>0.3810083333333333</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="125">
@@ -30604,7 +30604,7 @@
         <v>45748</v>
       </c>
       <c r="B125" t="n">
-        <v>0.3614694444444445</v>
+        <v>361.47</v>
       </c>
     </row>
     <row r="126">
@@ -30612,7 +30612,7 @@
         <v>45778</v>
       </c>
       <c r="B126" t="n">
-        <v>0.4200861111111111</v>
+        <v>420.09</v>
       </c>
     </row>
     <row r="127">
@@ -30620,7 +30620,7 @@
         <v>45809</v>
       </c>
       <c r="B127" t="n">
-        <v>0.3810083333333333</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="128">
@@ -30628,7 +30628,7 @@
         <v>45839</v>
       </c>
       <c r="B128" t="n">
-        <v>0.4005472222222222</v>
+        <v>400.55</v>
       </c>
     </row>
     <row r="129">
@@ -30636,7 +30636,7 @@
         <v>45870</v>
       </c>
       <c r="B129" t="n">
-        <v>0.3907777777777778</v>
+        <v>390.78</v>
       </c>
     </row>
     <row r="130">
@@ -30644,7 +30644,7 @@
         <v>45901</v>
       </c>
       <c r="B130" t="n">
-        <v>0.3614694444444445</v>
+        <v>361.47</v>
       </c>
     </row>
     <row r="131">
@@ -30652,7 +30652,7 @@
         <v>45931</v>
       </c>
       <c r="B131" t="n">
-        <v>0.3712388888888889</v>
+        <v>371.24</v>
       </c>
     </row>
     <row r="132">
@@ -30660,7 +30660,7 @@
         <v>45962</v>
       </c>
       <c r="B132" t="n">
-        <v>0.3712388888888889</v>
+        <v>371.24</v>
       </c>
     </row>
     <row r="133">
@@ -30668,7 +30668,7 @@
         <v>45992</v>
       </c>
       <c r="B133" t="n">
-        <v>0.3810083333333333</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="134">
@@ -30676,7 +30676,7 @@
         <v>46023</v>
       </c>
       <c r="B134" t="n">
-        <v>0.3712388888888889</v>
+        <v>371.24</v>
       </c>
     </row>
     <row r="135">
@@ -30684,7 +30684,7 @@
         <v>46054</v>
       </c>
       <c r="B135" t="n">
-        <v>0.3419305555555555</v>
+        <v>341.93</v>
       </c>
     </row>
     <row r="136">
@@ -30692,7 +30692,7 @@
         <v>46082</v>
       </c>
       <c r="B136" t="n">
-        <v>0.4103166666666667</v>
+        <v>410.32</v>
       </c>
     </row>
     <row r="137">
@@ -30700,7 +30700,7 @@
         <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>0.3712388888888889</v>
+        <v>371.24</v>
       </c>
     </row>
     <row r="138">
@@ -30708,7 +30708,7 @@
         <v>46143</v>
       </c>
       <c r="B138" t="n">
-        <v>0.4005472222222222</v>
+        <v>400.55</v>
       </c>
     </row>
     <row r="139">
@@ -30716,7 +30716,7 @@
         <v>46174</v>
       </c>
       <c r="B139" t="n">
-        <v>0.3907777777777778</v>
+        <v>390.78</v>
       </c>
     </row>
     <row r="140">
@@ -30724,7 +30724,7 @@
         <v>46204</v>
       </c>
       <c r="B140" t="n">
-        <v>0.4103166666666667</v>
+        <v>410.32</v>
       </c>
     </row>
     <row r="141">
@@ -30732,7 +30732,7 @@
         <v>46235</v>
       </c>
       <c r="B141" t="n">
-        <v>0.3810083333333333</v>
+        <v>381.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/europe_biomethane_operators.xlsx
+++ b/output/Data and Chart Outputs/europe_biomethane_operators.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Biomethane injected into the gas grids (operator / statistical data) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -768,7 +769,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-05 03:11 UTC</t>
+          <t>2026-10-28 00:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2311,7 @@
         <v>0.6745890000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>0.37124</v>
+        <v>0.40055</v>
       </c>
     </row>
     <row r="135">
@@ -2324,7 +2325,7 @@
         <v>0.634038</v>
       </c>
       <c r="D135" t="n">
-        <v>0.34193</v>
+        <v>0.3517</v>
       </c>
     </row>
     <row r="136">
@@ -2352,7 +2353,7 @@
         <v>0.7226359999999999</v>
       </c>
       <c r="D137" t="n">
-        <v>0.37124</v>
+        <v>0.36147</v>
       </c>
     </row>
     <row r="138">
@@ -2366,7 +2367,7 @@
         <v>0.757698</v>
       </c>
       <c r="D138" t="n">
-        <v>0.40055</v>
+        <v>0.39078</v>
       </c>
     </row>
     <row r="139">
@@ -2380,7 +2381,7 @@
         <v>0.7310399999999999</v>
       </c>
       <c r="D139" t="n">
-        <v>0.39078</v>
+        <v>0.38101</v>
       </c>
     </row>
     <row r="140">
@@ -2394,7 +2395,7 @@
         <v>0.7862210000000001</v>
       </c>
       <c r="D140" t="n">
-        <v>0.41032</v>
+        <v>0.39078</v>
       </c>
     </row>
     <row r="141">
@@ -2408,7 +2409,7 @@
         <v>0.768591</v>
       </c>
       <c r="D141" t="n">
-        <v>0.38101</v>
+        <v>0.36147</v>
       </c>
     </row>
     <row r="142">
@@ -2416,10 +2417,13 @@
         <v>46266</v>
       </c>
       <c r="B142" t="n">
-        <v>1.138534</v>
+        <v>1.20544</v>
       </c>
       <c r="C142" t="n">
         <v>0.770609</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.31262</v>
       </c>
     </row>
   </sheetData>
@@ -2434,7 +2438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2469"/>
+  <dimension ref="A1:D2492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36694,10 +36698,10 @@
         <v>46276</v>
       </c>
       <c r="B2447" t="n">
-        <v>37.54</v>
+        <v>41.638</v>
       </c>
       <c r="C2447" t="n">
-        <v>7.462</v>
+        <v>8.493</v>
       </c>
       <c r="D2447" t="n">
         <v>26.634</v>
@@ -36708,10 +36712,10 @@
         <v>46277</v>
       </c>
       <c r="B2448" t="n">
-        <v>39.719</v>
+        <v>41.312</v>
       </c>
       <c r="C2448" t="n">
-        <v>7.47</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="D2448" t="n">
         <v>26.875</v>
@@ -36722,10 +36726,10 @@
         <v>46278</v>
       </c>
       <c r="B2449" t="n">
-        <v>39.351</v>
+        <v>40.856</v>
       </c>
       <c r="C2449" t="n">
-        <v>7.433</v>
+        <v>8.334</v>
       </c>
       <c r="D2449" t="n">
         <v>26.126</v>
@@ -36736,10 +36740,10 @@
         <v>46279</v>
       </c>
       <c r="B2450" t="n">
-        <v>39.526</v>
+        <v>40.794</v>
       </c>
       <c r="C2450" t="n">
-        <v>6.997</v>
+        <v>7.917</v>
       </c>
       <c r="D2450" t="n">
         <v>25.518</v>
@@ -36750,10 +36754,10 @@
         <v>46280</v>
       </c>
       <c r="B2451" t="n">
-        <v>39.168</v>
+        <v>40.941</v>
       </c>
       <c r="C2451" t="n">
-        <v>7.142</v>
+        <v>8.116</v>
       </c>
       <c r="D2451" t="n">
         <v>25.516</v>
@@ -36764,10 +36768,10 @@
         <v>46281</v>
       </c>
       <c r="B2452" t="n">
-        <v>39.639</v>
+        <v>41.494</v>
       </c>
       <c r="C2452" t="n">
-        <v>7.294</v>
+        <v>8.301</v>
       </c>
       <c r="D2452" t="n">
         <v>24.766</v>
@@ -36778,10 +36782,10 @@
         <v>46282</v>
       </c>
       <c r="B2453" t="n">
-        <v>38.196</v>
+        <v>42.098</v>
       </c>
       <c r="C2453" t="n">
-        <v>7.644</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D2453" t="n">
         <v>25.56</v>
@@ -36792,10 +36796,10 @@
         <v>46283</v>
       </c>
       <c r="B2454" t="n">
-        <v>38.554</v>
+        <v>42.555</v>
       </c>
       <c r="C2454" t="n">
-        <v>7.677</v>
+        <v>8.675000000000001</v>
       </c>
       <c r="D2454" t="n">
         <v>25.861</v>
@@ -36806,10 +36810,10 @@
         <v>46284</v>
       </c>
       <c r="B2455" t="n">
-        <v>38.206</v>
+        <v>42.091</v>
       </c>
       <c r="C2455" t="n">
-        <v>7.596</v>
+        <v>8.611000000000001</v>
       </c>
       <c r="D2455" t="n">
         <v>26.127</v>
@@ -36820,10 +36824,10 @@
         <v>46285</v>
       </c>
       <c r="B2456" t="n">
-        <v>37.639</v>
+        <v>41.295</v>
       </c>
       <c r="C2456" t="n">
-        <v>7.429</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D2456" t="n">
         <v>25.704</v>
@@ -36834,10 +36838,10 @@
         <v>46286</v>
       </c>
       <c r="B2457" t="n">
-        <v>38.24</v>
+        <v>42.035</v>
       </c>
       <c r="C2457" t="n">
-        <v>7.459</v>
+        <v>8.414999999999999</v>
       </c>
       <c r="D2457" t="n">
         <v>25.006</v>
@@ -36848,10 +36852,10 @@
         <v>46287</v>
       </c>
       <c r="B2458" t="n">
-        <v>39.046</v>
+        <v>41.647</v>
       </c>
       <c r="C2458" t="n">
-        <v>7.184</v>
+        <v>8.247999999999999</v>
       </c>
       <c r="D2458" t="n">
         <v>25.968</v>
@@ -36862,10 +36866,10 @@
         <v>46288</v>
       </c>
       <c r="B2459" t="n">
-        <v>37.835</v>
+        <v>41.865</v>
       </c>
       <c r="C2459" t="n">
-        <v>7.29</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="D2459" t="n">
         <v>26.243</v>
@@ -36876,10 +36880,10 @@
         <v>46289</v>
       </c>
       <c r="B2460" t="n">
-        <v>37.868</v>
+        <v>41.979</v>
       </c>
       <c r="C2460" t="n">
-        <v>7.391</v>
+        <v>8.493</v>
       </c>
       <c r="D2460" t="n">
         <v>25.715</v>
@@ -36890,10 +36894,10 @@
         <v>46290</v>
       </c>
       <c r="B2461" t="n">
-        <v>37.937</v>
+        <v>42.078</v>
       </c>
       <c r="C2461" t="n">
-        <v>7.325</v>
+        <v>8.33</v>
       </c>
       <c r="D2461" t="n">
         <v>27.27</v>
@@ -36904,10 +36908,10 @@
         <v>46291</v>
       </c>
       <c r="B2462" t="n">
-        <v>37.582</v>
+        <v>41.739</v>
       </c>
       <c r="C2462" t="n">
-        <v>7.301</v>
+        <v>8.250999999999999</v>
       </c>
       <c r="D2462" t="n">
         <v>26.72</v>
@@ -36918,10 +36922,10 @@
         <v>46292</v>
       </c>
       <c r="B2463" t="n">
-        <v>37.079</v>
+        <v>41.185</v>
       </c>
       <c r="C2463" t="n">
-        <v>7.251</v>
+        <v>8.193</v>
       </c>
       <c r="D2463" t="n">
         <v>26.585</v>
@@ -36932,10 +36936,10 @@
         <v>46293</v>
       </c>
       <c r="B2464" t="n">
-        <v>37.195</v>
+        <v>41.51</v>
       </c>
       <c r="C2464" t="n">
-        <v>7.122</v>
+        <v>8.058</v>
       </c>
       <c r="D2464" t="n">
         <v>26.055</v>
@@ -36946,10 +36950,10 @@
         <v>46294</v>
       </c>
       <c r="B2465" t="n">
-        <v>37.193</v>
+        <v>41.353</v>
       </c>
       <c r="C2465" t="n">
-        <v>7.046</v>
+        <v>7.952</v>
       </c>
       <c r="D2465" t="n">
         <v>26.124</v>
@@ -36960,10 +36964,10 @@
         <v>46295</v>
       </c>
       <c r="B2466" t="n">
-        <v>37.369</v>
+        <v>41.323</v>
       </c>
       <c r="C2466" t="n">
-        <v>7.303</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="D2466" t="n">
         <v>26.86</v>
@@ -36974,10 +36978,10 @@
         <v>46296</v>
       </c>
       <c r="B2467" t="n">
-        <v>38.816</v>
+        <v>39.15</v>
       </c>
       <c r="C2467" t="n">
-        <v>7.412</v>
+        <v>7.411</v>
       </c>
       <c r="D2467" t="n">
         <v>26.99</v>
@@ -36988,10 +36992,10 @@
         <v>46297</v>
       </c>
       <c r="B2468" t="n">
-        <v>39.062</v>
+        <v>39.438</v>
       </c>
       <c r="C2468" t="n">
-        <v>7.529</v>
+        <v>7.528</v>
       </c>
       <c r="D2468" t="n">
         <v>27.329</v>
@@ -37001,8 +37005,330 @@
       <c r="A2469" s="4" t="n">
         <v>46298</v>
       </c>
+      <c r="B2469" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="C2469" t="n">
+        <v>7.519</v>
+      </c>
       <c r="D2469" t="n">
         <v>27.207</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2470" t="n">
+        <v>38.107</v>
+      </c>
+      <c r="C2470" t="n">
+        <v>7.371</v>
+      </c>
+      <c r="D2470" t="n">
+        <v>26.32</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2471" t="n">
+        <v>38.418</v>
+      </c>
+      <c r="C2471" t="n">
+        <v>7.434</v>
+      </c>
+      <c r="D2471" t="n">
+        <v>26.054</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2472" t="n">
+        <v>38.185</v>
+      </c>
+      <c r="C2472" t="n">
+        <v>7.198</v>
+      </c>
+      <c r="D2472" t="n">
+        <v>25.499</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2473" t="n">
+        <v>38.757</v>
+      </c>
+      <c r="C2473" t="n">
+        <v>7.438</v>
+      </c>
+      <c r="D2473" t="n">
+        <v>26.049</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2474" t="n">
+        <v>36.883</v>
+      </c>
+      <c r="C2474" t="n">
+        <v>7.479</v>
+      </c>
+      <c r="D2474" t="n">
+        <v>26.36</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2475" t="n">
+        <v>39.014</v>
+      </c>
+      <c r="C2475" t="n">
+        <v>7.496</v>
+      </c>
+      <c r="D2475" t="n">
+        <v>27.273</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2476" t="n">
+        <v>38.556</v>
+      </c>
+      <c r="C2476" t="n">
+        <v>7.567</v>
+      </c>
+      <c r="D2476" t="n">
+        <v>27.352</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2477" t="n">
+        <v>37.793</v>
+      </c>
+      <c r="C2477" t="n">
+        <v>7.435</v>
+      </c>
+      <c r="D2477" t="n">
+        <v>26.944</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2478" t="n">
+        <v>38.183</v>
+      </c>
+      <c r="C2478" t="n">
+        <v>7.462</v>
+      </c>
+      <c r="D2478" t="n">
+        <v>26.111</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2479" t="n">
+        <v>37.996</v>
+      </c>
+      <c r="C2479" t="n">
+        <v>7.277</v>
+      </c>
+      <c r="D2479" t="n">
+        <v>26.445</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2480" t="n">
+        <v>38.353</v>
+      </c>
+      <c r="C2480" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="D2480" t="n">
+        <v>27.098</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2481" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="C2481" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="D2481" t="n">
+        <v>27.438</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2482" t="n">
+        <v>38.988</v>
+      </c>
+      <c r="C2482" t="n">
+        <v>7.482</v>
+      </c>
+      <c r="D2482" t="n">
+        <v>27.407</v>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2483" t="n">
+        <v>38.834</v>
+      </c>
+      <c r="C2483" t="n">
+        <v>7.476</v>
+      </c>
+      <c r="D2483" t="n">
+        <v>27.527</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2484" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="C2484" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="D2484" t="n">
+        <v>27.052</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2485" t="n">
+        <v>38.082</v>
+      </c>
+      <c r="C2485" t="n">
+        <v>7.514</v>
+      </c>
+      <c r="D2485" t="n">
+        <v>26.221</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2486" t="n">
+        <v>37.884</v>
+      </c>
+      <c r="C2486" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="D2486" t="n">
+        <v>25.703</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2487" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="C2487" t="n">
+        <v>7.396</v>
+      </c>
+      <c r="D2487" t="n">
+        <v>25.891</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>37.832</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>26.236</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>6.916</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>26.791</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>39.116</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>7.509</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>27.856</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>36.962</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>7.321</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>24.918</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>25.471</v>
       </c>
     </row>
   </sheetData>
@@ -37016,7 +37342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38092,7 +38418,7 @@
         <v>46023</v>
       </c>
       <c r="B134" t="n">
-        <v>371.24</v>
+        <v>400.55</v>
       </c>
     </row>
     <row r="135">
@@ -38100,7 +38426,7 @@
         <v>46054</v>
       </c>
       <c r="B135" t="n">
-        <v>341.93</v>
+        <v>351.7</v>
       </c>
     </row>
     <row r="136">
@@ -38116,7 +38442,7 @@
         <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>371.24</v>
+        <v>361.47</v>
       </c>
     </row>
     <row r="138">
@@ -38124,7 +38450,7 @@
         <v>46143</v>
       </c>
       <c r="B138" t="n">
-        <v>400.55</v>
+        <v>390.78</v>
       </c>
     </row>
     <row r="139">
@@ -38132,7 +38458,7 @@
         <v>46174</v>
       </c>
       <c r="B139" t="n">
-        <v>390.78</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="140">
@@ -38140,7 +38466,7 @@
         <v>46204</v>
       </c>
       <c r="B140" t="n">
-        <v>410.32</v>
+        <v>390.78</v>
       </c>
     </row>
     <row r="141">
@@ -38148,7 +38474,15 @@
         <v>46235</v>
       </c>
       <c r="B141" t="n">
-        <v>381.01</v>
+        <v>361.47</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B142" t="n">
+        <v>312.62</v>
       </c>
     </row>
   </sheetData>
